--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N41_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>88.65757084326006</v>
+        <v>14.40685526202976</v>
       </c>
       <c r="D2" t="n">
-        <v>84.75017342715586</v>
+        <v>13.77190318191283</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
